--- a/survey_templates/048_corporate_diversity_training_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/048_corporate_diversity_training_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_not_at_all_satisfied'}</t>
+          <t>1_-_not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '1 - Not at all satisfied'}</t>
+          <t>1 - Not at all satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_dissatisfied'}</t>
+          <t>2_-_somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat dissatisfied'}</t>
+          <t>2 - Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_satisfied'}</t>
+          <t>4_-_somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat satisfied'}</t>
+          <t>4 - Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_satisfied'}</t>
+          <t>5_-_very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very satisfied'}</t>
+          <t>5 - Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_relevant'}</t>
+          <t>not_relevant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not relevant'}</t>
+          <t>Not relevant</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_relevant'}</t>
+          <t>somewhat_relevant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat relevant'}</t>
+          <t>Somewhat relevant</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_relevant'}</t>
+          <t>very_relevant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat relevant'}</t>
+          <t>Very relevant</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_relevant'}</t>
+          <t>1_-_not_at_all_likely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very relevant'}</t>
+          <t>1 - Not at all likely</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_not_at_all_likely'}</t>
+          <t>2_-_somewhat_likely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '1 - Not at all likely'}</t>
+          <t>2 - Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_likely'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat likely'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>4_-_somewhat_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>4 - Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_likely'}</t>
+          <t>5_-_very_likely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat likely'}</t>
+          <t>5 - Very likely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_likely'}</t>
+          <t>1_-_not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very likely'}</t>
+          <t>1 - Not at all satisfied</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_not_at_all_satisfied'}</t>
+          <t>2_-_somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '1 - Not at all satisfied'}</t>
+          <t>2 - Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_dissatisfied'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat dissatisfied'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>4_-_somewhat_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>4 - Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_satisfied'}</t>
+          <t>5_-_very_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat satisfied'}</t>
+          <t>5 - Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_satisfied'}</t>
+          <t>1_-_not_at_all_likely</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very satisfied'}</t>
+          <t>1 - Not at all likely</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_not_at_all_likely'}</t>
+          <t>2_-_somewhat_likely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': '1 - Not at all likely'}</t>
+          <t>2 - Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_likely'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat likely'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>4_-_somewhat_likely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>4 - Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_likely'}</t>
+          <t>5_-_very_likely</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat likely'}</t>
+          <t>5 - Very likely</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_likely'}</t>
+          <t>1_-_not_at_all_likely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very likely'}</t>
+          <t>1 - Not at all likely</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_not_at_all_likely'}</t>
+          <t>2_-_somewhat_likely</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': '1 - Not at all likely'}</t>
+          <t>2 - Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_likely'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat likely'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>4_-_somewhat_likely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>4 - Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_likely'}</t>
+          <t>5_-_very_likely</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat likely'}</t>
+          <t>5 - Very likely</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_19_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_likely'}</t>
+          <t>2_or_more_breaks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very likely'}</t>
+          <t>2 or more breaks</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'2_or_more_breaks'}</t>
+          <t>fewer_than_2_breaks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': '2 or more breaks'}</t>
+          <t>Fewer than 2 breaks</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'fewer_than_2_breaks'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Fewer than 2 breaks'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>page_19_choices</t>
+          <t>page_20_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>very_comfortable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>Very comfortable</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'very_comfortable'}</t>
+          <t>somewhat_comfortable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Very comfortable'}</t>
+          <t>Somewhat comfortable</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_comfortable'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat comfortable'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_uncomfortable</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat uncomfortable</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_uncomfortable'}</t>
+          <t>very_uncomfortable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat uncomfortable'}</t>
+          <t>Very uncomfortable</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_21_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'very_uncomfortable'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Very uncomfortable'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_22_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'partially'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Partially'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_23_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'partially'}</t>
+          <t>very_clear</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Partially'}</t>
+          <t>Very clear</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'very_clear'}</t>
+          <t>somewhat_clear</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Very clear'}</t>
+          <t>Somewhat clear</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_clear'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat clear'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_unclear</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat unclear</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unclear'}</t>
+          <t>very_unclear</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat unclear'}</t>
+          <t>Very unclear</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>page_23_choices</t>
+          <t>page_24_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'very_unclear'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Very unclear'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>page_24_choices</t>
+          <t>page_25_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'partially'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Partially'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2032,29 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>page_25_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>{'label':_'partially'}</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>{'label': 'Partially'}</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
